--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 522 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 691 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="30">

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 691 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 522 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="30">

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Idéalement situé dans le 16eme arrondissement de Paris, ce local commercial bénéficie d’un environnement recherché, caractérisé par son calme, son élégance et son architecture remarquable. Ce secteur prisé, bien desservi par les transports en commun, offre un cadre de vie agréable et dynamique, parfait pour une activité commerciale. Caractéristiques du bien : - Surface commerciale en rez-de-chaussée avec une belle vitrine offrant une visibilité optimale (18,44 m2). - Studio et/ou bureau au 1er étage, idéal pour un usage privé ou un bureau (18,69 m2). - Zone de stockage en sous-sol, chauffée et parfaitement exploitable (13,7 m2). Deux escaliers desservent les trois niveaux, facilitant la circulation et l’aménagement des espaces. Ce bien rare sur le marché combine une localisation stratégique et un agencement fonctionnel, parfait pour toute activité nécessitant un espace de vente, un bureau indépendant et une zone de stockage efficace. Les honoraires sont à la charge de l'acquéreur. DPE C - GES B. Bien soumis au régime de la copropriété. Charges annuelles de 1228€. Pas de procédure en cours. Contactez Maxime Ramond Bluzet pour plus d’informations ou organiser une visite : / REF MR-6892-2 Honoraires inclus de 4.29% à la charge de l'acquéreur. Prix hors honoraires 350 000 €. Dans une copropriété de 65 lots. Quote-part moyenne du budget prévisionnel 1 228 €/an. Procédure en cours : 39/2173. Classe énergie C, Classe climat A. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : https://www.georisques.gouv.fr.</t>
+          <t>Idéalement situé dans le 16eme arrondissement de Paris, ce local commercial bénéficie d'un environnement recherché, caractérisé par son calme, son élégance et son architecture remarquable. Ce secteur prisé, bien desservi par les transports en commun, offre un cadre de vie agréable et dynamique, parfait pour une activité commerciale. Caractéristiques du bien : - Surface commerciale en rez-de-chaussée avec une belle vitrine offrant une visibilité optimale (18,44 m2). - Studio et/ou bureau au 1er étage, idéal pour un usage privé ou un bureau (18,69 m2). - Zone de stockage en sous-sol, chauffée et parfaitement exploitable (13,7 m2). Deux escaliers desservent les trois niveaux, facilitant la circulation et l'aménagement des espaces. Ce bien rare sur le marché combine une localisation stratégique et un agencement fonctionnel, parfait pour toute activité nécessitant un espace de vente, un bureau indépendant et une zone de stockage efficace. Les honoraires sont à la charge de l'acquéreur. DPE C - GES B. Bien soumis au régime de la copropriété. Charges annuelles de 1228€. Pas de procédure en cours. Contactez Maxime Ramond Bluzet pour plus d'informations ou organiser une visite : maxime@cesaretbrutus.com / 06 48 14 62 71 REF MR-6892-2 Honoraires inclus de 4.29% à la charge de l'acquéreur. Prix hors honoraires 350 000 €. Dans une copropriété de 65 lots. Quote-part moyenne du budget prévisionnel 1 228 €/an. Procédure en cours : 39/2173. Classe énergie C, Classe climat A. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : georisques.gouv.fr.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 522 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 445 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="30">

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve</t>
+          <t>loyer_estime · rendement_anormalement_eleve · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
